--- a/models/data/field.xlsx
+++ b/models/data/field.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31F8667-4087-4795-812F-D7FB8AC4D77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2570DD-3201-42E7-A8D3-0CCF592BA086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="1995" windowWidth="22695" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="22695" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="岩座神農地" sheetId="1" r:id="rId1"/>
@@ -182,7 +182,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,25 +242,25 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,40 +580,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -635,16 +635,16 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
-      <c r="L2" s="16"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D3" s="14"/>
-      <c r="E3" s="15">
+      <c r="D3" s="11"/>
+      <c r="E3" s="12">
         <f>D3/100</f>
         <v>0</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15">
+      <c r="F3" s="11"/>
+      <c r="G3" s="12">
         <f>F3/100</f>
         <v>0</v>
       </c>

--- a/models/data/field.xlsx
+++ b/models/data/field.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2570DD-3201-42E7-A8D3-0CCF592BA086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F35280-09C8-46BE-B0ED-AFADC6A79999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="22695" windowHeight="13065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4605" yWindow="1680" windowWidth="23790" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="岩座神農地" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">岩座神農地!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">岩座神農地!$A$1:$M$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -126,6 +126,20 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>メンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中山間</t>
+    <rPh sb="0" eb="3">
+      <t>チュウサンカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細目書</t>
+    <rPh sb="0" eb="3">
+      <t>サイモクショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -567,19 +581,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.375" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="15" style="2" customWidth="1"/>
     <col min="4" max="7" width="11.25" style="3" customWidth="1"/>
-    <col min="8" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="4" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
+    <col min="8" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="4" customWidth="1"/>
+    <col min="14" max="14" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -608,16 +622,22 @@
         <v>4</v>
       </c>
       <c r="J1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="M1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="N1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="10"/>
       <c r="B2" s="5"/>
       <c r="C2" s="8"/>
@@ -635,9 +655,11 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
-      <c r="L2" s="13"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="13"/>
     </row>
-    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="11"/>
       <c r="E3" s="12">
         <f>D3/100</f>
@@ -650,7 +672,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
